--- a/grupos/2ALCV - Estadisticos 20212.xlsx
+++ b/grupos/2ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="168">
   <si>
     <t>Materia</t>
   </si>
@@ -203,24 +203,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -242,99 +242,216 @@
     <t>CABALLERO</t>
   </si>
   <si>
+    <t>ELPIDIO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>KATHIA</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
     <t>CORDOVA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>ESPIRITU</t>
   </si>
   <si>
-    <t>ELPIDIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
     <t>SOLANO</t>
   </si>
   <si>
     <t>SORIANO</t>
   </si>
   <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
     <t>VALENCIA</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
@@ -344,78 +461,27 @@
     <t>ARIAS</t>
   </si>
   <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>VALIENTE</t>
   </si>
   <si>
     <t>VICENTE</t>
   </si>
   <si>
-    <t>BRETON</t>
-  </si>
-  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
     <t>MENA</t>
   </si>
   <si>
     <t>PORRAS</t>
   </si>
   <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>MACARIO</t>
   </si>
   <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>KATHIA</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
     <t>CRISTAL YOSELIN</t>
   </si>
   <si>
@@ -425,100 +491,34 @@
     <t>EVELYN JOHANA</t>
   </si>
   <si>
-    <t>MARYFER</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
     <t>BERENICE</t>
   </si>
   <si>
     <t>ESTEFANIA</t>
   </si>
   <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
     <t>REGINA ISABEL</t>
   </si>
   <si>
     <t>VANESSA</t>
   </si>
   <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
     <t>FATIMA MARILYN</t>
   </si>
   <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
     <t>ITZEL ABIGAIL</t>
   </si>
   <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
     <t>CITLALI ESPERANZA</t>
   </si>
   <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
     <t>ANGELES</t>
   </si>
   <si>
     <t>KAREN</t>
   </si>
   <si>
-    <t>RUBI</t>
-  </si>
-  <si>
     <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>FLOR GUADALUPE</t>
@@ -1016,13 +1016,13 @@
         <v>9</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>7</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -1070,13 +1070,13 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1093,13 +1093,13 @@
         <v>-1</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>6</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1147,13 +1147,13 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1161,7 +1161,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -1170,13 +1170,13 @@
         <v>-1</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>7</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1215,7 +1215,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>7</v>
@@ -1224,13 +1224,13 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1238,7 +1238,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -1247,13 +1247,13 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F7">
         <v>8</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1292,7 +1292,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1301,13 +1301,13 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1315,10 +1315,10 @@
         <v>16</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1333,10 +1333,10 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1344,7 +1344,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -1353,13 +1353,13 @@
         <v>-1</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F9">
         <v>8</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1398,7 +1398,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1407,13 +1407,13 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1430,13 +1430,13 @@
         <v>-1</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F10">
         <v>8</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1484,13 +1484,13 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1507,7 +1507,7 @@
         <v>-1</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -1561,7 +1561,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -1575,7 +1575,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -1584,13 +1584,13 @@
         <v>10</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F12">
         <v>9</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1629,7 +1629,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -1638,13 +1638,13 @@
         <v>10</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1661,13 +1661,13 @@
         <v>-1</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F13">
         <v>6</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1715,13 +1715,13 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1738,13 +1738,13 @@
         <v>-1</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F14">
         <v>8</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1792,13 +1792,13 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1815,13 +1815,13 @@
         <v>-1</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1869,13 +1869,13 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1883,7 +1883,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C16">
         <v>8</v>
@@ -1892,13 +1892,13 @@
         <v>10</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F16">
         <v>10</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1937,7 +1937,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -1946,13 +1946,13 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X16">
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1960,7 +1960,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -1969,7 +1969,7 @@
         <v>-1</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>7</v>
@@ -2014,7 +2014,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -2023,7 +2023,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -2037,7 +2037,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>9</v>
@@ -2046,13 +2046,13 @@
         <v>10</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F18">
         <v>10</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2091,7 +2091,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -2100,13 +2100,13 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2114,7 +2114,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>7</v>
@@ -2123,13 +2123,13 @@
         <v>9</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F19">
         <v>9</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2168,7 +2168,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2177,13 +2177,13 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2191,7 +2191,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -2200,13 +2200,13 @@
         <v>10</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F20">
         <v>10</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2245,7 +2245,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2254,13 +2254,13 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2268,7 +2268,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>-1</v>
@@ -2277,13 +2277,13 @@
         <v>10</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F21">
         <v>8</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2322,7 +2322,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2331,13 +2331,13 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2345,7 +2345,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C22">
         <v>8</v>
@@ -2354,7 +2354,7 @@
         <v>10</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F22">
         <v>9</v>
@@ -2399,7 +2399,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2408,7 +2408,7 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2422,19 +2422,19 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>-1</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F23">
         <v>8</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2467,19 +2467,19 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2487,7 +2487,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C24">
         <v>7</v>
@@ -2496,13 +2496,13 @@
         <v>8</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F24">
         <v>9</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2541,7 +2541,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2550,13 +2550,13 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2573,13 +2573,13 @@
         <v>-1</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>9</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2627,13 +2627,13 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2641,7 +2641,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>10</v>
@@ -2650,13 +2650,13 @@
         <v>10</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F26">
         <v>10</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2695,7 +2695,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -2704,13 +2704,13 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2718,7 +2718,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C27">
         <v>7</v>
@@ -2727,7 +2727,7 @@
         <v>-1</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F27">
         <v>6</v>
@@ -2772,7 +2772,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>7</v>
@@ -2781,7 +2781,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -2795,7 +2795,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C28">
         <v>-1</v>
@@ -2804,7 +2804,7 @@
         <v>10</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F28">
         <v>8</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -2858,7 +2858,7 @@
         <v>10</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -2872,7 +2872,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C29">
         <v>8</v>
@@ -2881,13 +2881,13 @@
         <v>-1</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F29">
         <v>8</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -2926,7 +2926,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -2935,13 +2935,13 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2949,7 +2949,7 @@
         <v>38</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G30">
         <v>-1</v>
@@ -2967,7 +2967,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>-1</v>
@@ -2987,13 +2987,13 @@
         <v>-1</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F31">
         <v>8</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3041,13 +3041,13 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3055,7 +3055,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C32">
         <v>7</v>
@@ -3064,13 +3064,13 @@
         <v>-1</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F32">
         <v>8</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3109,7 +3109,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>7</v>
@@ -3118,13 +3118,13 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3141,13 +3141,13 @@
         <v>-1</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F33">
         <v>8</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3195,13 +3195,13 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3209,7 +3209,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>7</v>
@@ -3218,13 +3218,13 @@
         <v>8</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F34">
         <v>8</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H34">
         <v>-1</v>
@@ -3263,7 +3263,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>7</v>
@@ -3272,13 +3272,13 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3286,7 +3286,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C35">
         <v>8</v>
@@ -3295,13 +3295,13 @@
         <v>-1</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F35">
         <v>8</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H35">
         <v>-1</v>
@@ -3340,7 +3340,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>8</v>
@@ -3349,13 +3349,13 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3372,7 +3372,7 @@
         <v>8</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F36">
         <v>8</v>
@@ -3426,7 +3426,7 @@
         <v>8</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>8</v>
@@ -3449,13 +3449,13 @@
         <v>-1</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F37">
         <v>6</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H37">
         <v>-1</v>
@@ -3503,13 +3503,13 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3517,7 +3517,7 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C38">
         <v>7</v>
@@ -3526,13 +3526,13 @@
         <v>10</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F38">
         <v>9</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H38">
         <v>-1</v>
@@ -3571,7 +3571,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U38">
         <v>7</v>
@@ -3580,13 +3580,13 @@
         <v>10</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X38">
         <v>9</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3594,7 +3594,7 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C39">
         <v>8</v>
@@ -3603,13 +3603,13 @@
         <v>10</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F39">
         <v>10</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H39">
         <v>-1</v>
@@ -3648,7 +3648,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U39">
         <v>8</v>
@@ -3657,13 +3657,13 @@
         <v>10</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X39">
         <v>10</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3680,7 +3680,7 @@
         <v>-1</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F40">
         <v>9</v>
@@ -3734,7 +3734,7 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>9</v>
@@ -3748,10 +3748,10 @@
         <v>49</v>
       </c>
       <c r="E41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K41">
         <v>-1</v>
@@ -3766,10 +3766,10 @@
         <v>-1</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3786,13 +3786,13 @@
         <v>-1</v>
       </c>
       <c r="E42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F42">
         <v>8</v>
       </c>
       <c r="G42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H42">
         <v>-1</v>
@@ -3840,13 +3840,13 @@
         <v>-1</v>
       </c>
       <c r="W42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X42">
         <v>8</v>
       </c>
       <c r="Y42">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -3854,7 +3854,7 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C43">
         <v>8</v>
@@ -3863,13 +3863,13 @@
         <v>7</v>
       </c>
       <c r="E43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F43">
         <v>10</v>
       </c>
       <c r="G43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H43">
         <v>-1</v>
@@ -3908,7 +3908,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U43">
         <v>8</v>
@@ -3917,13 +3917,13 @@
         <v>7</v>
       </c>
       <c r="W43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X43">
         <v>10</v>
       </c>
       <c r="Y43">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3979,7 +3979,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -3988,56 +3988,62 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>45.95</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>9.199999999999999</v>
+      </c>
       <c r="I2">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>54.05</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>62.16</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
       <c r="I3">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -4046,112 +4052,115 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>7.5</v>
+      </c>
       <c r="I4">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>45.95</v>
+        <v>88.89</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>54.05</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>94.59</v>
+      </c>
+      <c r="G6">
+        <v>5.41</v>
+      </c>
+      <c r="H6">
+        <v>8.1</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>88.89</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>7.6</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>11.11</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4167,7 +4176,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4202,93 +4211,93 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920071</v>
+        <v>21330051920072</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920071</v>
+        <v>21330051920357</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920072</v>
+        <v>21330051920357</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920072</v>
+        <v>21330051920108</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>61</v>
@@ -4296,79 +4305,79 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920072</v>
+        <v>21330051920108</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920072</v>
+        <v>21330051920108</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920357</v>
+        <v>21330051920108</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920357</v>
+        <v>21330051920076</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>61</v>
@@ -4376,19 +4385,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920357</v>
+        <v>21330051920076</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
         <v>62</v>
@@ -4396,119 +4405,119 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920357</v>
+        <v>21330051920077</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920074</v>
+        <v>21330051920077</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920074</v>
+        <v>21330051920078</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920074</v>
+        <v>21330051920078</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920378</v>
+        <v>21330051920080</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920378</v>
+        <v>21330051920080</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>63</v>
@@ -4516,19 +4525,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920075</v>
+        <v>21330051920082</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
         <v>61</v>
@@ -4536,39 +4545,39 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920075</v>
+        <v>21330051920085</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920075</v>
+        <v>21330051920086</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>63</v>
@@ -4576,99 +4585,99 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920108</v>
+        <v>20330051920302</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920108</v>
+        <v>21330051920092</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920108</v>
+        <v>21330051920092</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
         <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920108</v>
+        <v>21330051920094</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
         <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920108</v>
+        <v>21330051920094</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
         <v>101</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
         <v>63</v>
@@ -4676,39 +4685,39 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920076</v>
+        <v>21330051920096</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920076</v>
+        <v>21330051920097</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E27" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F27" t="s">
         <v>61</v>
@@ -4716,39 +4725,39 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920076</v>
+        <v>21330051920097</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920076</v>
+        <v>18330051920296</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
         <v>63</v>
@@ -4756,119 +4765,119 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920077</v>
+        <v>21330051920098</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s">
         <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920077</v>
+        <v>21330051920098</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s">
         <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920077</v>
+        <v>21330051920099</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920077</v>
+        <v>21330051920100</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920078</v>
+        <v>21330051920100</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920078</v>
+        <v>21330051920383</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E35" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F35" t="s">
         <v>61</v>
@@ -4876,19 +4885,19 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920078</v>
+        <v>21330051920102</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F36" t="s">
         <v>62</v>
@@ -4896,19 +4905,19 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920078</v>
+        <v>21330051920102</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
         <v>63</v>
@@ -4916,19 +4925,19 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920079</v>
+        <v>21330051920103</v>
       </c>
       <c r="B38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" t="s">
         <v>79</v>
       </c>
-      <c r="C38" t="s">
-        <v>110</v>
-      </c>
       <c r="D38" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E38" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F38" t="s">
         <v>61</v>
@@ -4936,19 +4945,19 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920079</v>
+        <v>21330051920103</v>
       </c>
       <c r="B39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" t="s">
         <v>79</v>
       </c>
-      <c r="C39" t="s">
-        <v>110</v>
-      </c>
       <c r="D39" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F39" t="s">
         <v>62</v>
@@ -4956,59 +4965,59 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>21330051920079</v>
+        <v>21330051920104</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D40" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F40" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920080</v>
+        <v>21330051920104</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E41" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F41" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920080</v>
+        <v>21330051920107</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C42" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D42" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E42" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F42" t="s">
         <v>61</v>
@@ -5016,19 +5025,19 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920080</v>
+        <v>21330051920107</v>
       </c>
       <c r="B43" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C43" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D43" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F43" t="s">
         <v>62</v>
@@ -5036,19 +5045,19 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920080</v>
+        <v>21330051920107</v>
       </c>
       <c r="B44" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C44" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D44" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E44" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
         <v>63</v>
@@ -5056,19 +5065,19 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920081</v>
+        <v>21330051920109</v>
       </c>
       <c r="B45" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C45" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D45" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E45" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F45" t="s">
         <v>61</v>
@@ -5076,1942 +5085,42 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>21330051920081</v>
+        <v>21330051920109</v>
       </c>
       <c r="B46" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C46" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D46" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E46" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F46" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>21330051920081</v>
+        <v>21330051920109</v>
       </c>
       <c r="B47" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D47" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E47" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F47" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920082</v>
-      </c>
-      <c r="B48" t="s">
-        <v>81</v>
-      </c>
-      <c r="C48" t="s">
-        <v>112</v>
-      </c>
-      <c r="D48" t="s">
-        <v>141</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920082</v>
-      </c>
-      <c r="B49" t="s">
-        <v>81</v>
-      </c>
-      <c r="C49" t="s">
-        <v>112</v>
-      </c>
-      <c r="D49" t="s">
-        <v>141</v>
-      </c>
-      <c r="E49" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920082</v>
-      </c>
-      <c r="B50" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" t="s">
-        <v>112</v>
-      </c>
-      <c r="D50" t="s">
-        <v>141</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920082</v>
-      </c>
-      <c r="B51" t="s">
-        <v>81</v>
-      </c>
-      <c r="C51" t="s">
-        <v>112</v>
-      </c>
-      <c r="D51" t="s">
-        <v>141</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920083</v>
-      </c>
-      <c r="B52" t="s">
-        <v>82</v>
-      </c>
-      <c r="C52" t="s">
-        <v>81</v>
-      </c>
-      <c r="D52" t="s">
-        <v>142</v>
-      </c>
-      <c r="E52" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920083</v>
-      </c>
-      <c r="B53" t="s">
-        <v>82</v>
-      </c>
-      <c r="C53" t="s">
-        <v>81</v>
-      </c>
-      <c r="D53" t="s">
-        <v>142</v>
-      </c>
-      <c r="E53" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920083</v>
-      </c>
-      <c r="B54" t="s">
-        <v>82</v>
-      </c>
-      <c r="C54" t="s">
-        <v>81</v>
-      </c>
-      <c r="D54" t="s">
-        <v>142</v>
-      </c>
-      <c r="E54" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920084</v>
-      </c>
-      <c r="B55" t="s">
-        <v>83</v>
-      </c>
-      <c r="C55" t="s">
-        <v>113</v>
-      </c>
-      <c r="D55" t="s">
-        <v>143</v>
-      </c>
-      <c r="E55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920084</v>
-      </c>
-      <c r="B56" t="s">
-        <v>83</v>
-      </c>
-      <c r="C56" t="s">
-        <v>113</v>
-      </c>
-      <c r="D56" t="s">
-        <v>143</v>
-      </c>
-      <c r="E56" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920084</v>
-      </c>
-      <c r="B57" t="s">
-        <v>83</v>
-      </c>
-      <c r="C57" t="s">
-        <v>113</v>
-      </c>
-      <c r="D57" t="s">
-        <v>143</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920085</v>
-      </c>
-      <c r="B58" t="s">
-        <v>84</v>
-      </c>
-      <c r="C58" t="s">
-        <v>109</v>
-      </c>
-      <c r="D58" t="s">
-        <v>144</v>
-      </c>
-      <c r="E58" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920085</v>
-      </c>
-      <c r="B59" t="s">
-        <v>84</v>
-      </c>
-      <c r="C59" t="s">
-        <v>109</v>
-      </c>
-      <c r="D59" t="s">
-        <v>144</v>
-      </c>
-      <c r="E59" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920085</v>
-      </c>
-      <c r="B60" t="s">
-        <v>84</v>
-      </c>
-      <c r="C60" t="s">
-        <v>109</v>
-      </c>
-      <c r="D60" t="s">
-        <v>144</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920085</v>
-      </c>
-      <c r="B61" t="s">
-        <v>84</v>
-      </c>
-      <c r="C61" t="s">
-        <v>109</v>
-      </c>
-      <c r="D61" t="s">
-        <v>144</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920086</v>
-      </c>
-      <c r="B62" t="s">
-        <v>84</v>
-      </c>
-      <c r="C62" t="s">
-        <v>114</v>
-      </c>
-      <c r="D62" t="s">
-        <v>145</v>
-      </c>
-      <c r="E62" t="s">
-        <v>5</v>
-      </c>
-      <c r="F62" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920086</v>
-      </c>
-      <c r="B63" t="s">
-        <v>84</v>
-      </c>
-      <c r="C63" t="s">
-        <v>114</v>
-      </c>
-      <c r="D63" t="s">
-        <v>145</v>
-      </c>
-      <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920086</v>
-      </c>
-      <c r="B64" t="s">
-        <v>84</v>
-      </c>
-      <c r="C64" t="s">
-        <v>114</v>
-      </c>
-      <c r="D64" t="s">
-        <v>145</v>
-      </c>
-      <c r="E64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>20330051920302</v>
-      </c>
-      <c r="B65" t="s">
-        <v>84</v>
-      </c>
-      <c r="C65" t="s">
-        <v>115</v>
-      </c>
-      <c r="D65" t="s">
-        <v>146</v>
-      </c>
-      <c r="E65" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>20330051920302</v>
-      </c>
-      <c r="B66" t="s">
-        <v>84</v>
-      </c>
-      <c r="C66" t="s">
-        <v>115</v>
-      </c>
-      <c r="D66" t="s">
-        <v>146</v>
-      </c>
-      <c r="E66" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>20330051920302</v>
-      </c>
-      <c r="B67" t="s">
-        <v>84</v>
-      </c>
-      <c r="C67" t="s">
-        <v>115</v>
-      </c>
-      <c r="D67" t="s">
-        <v>146</v>
-      </c>
-      <c r="E67" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>20330051920302</v>
-      </c>
-      <c r="B68" t="s">
-        <v>84</v>
-      </c>
-      <c r="C68" t="s">
-        <v>115</v>
-      </c>
-      <c r="D68" t="s">
-        <v>146</v>
-      </c>
-      <c r="E68" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920089</v>
-      </c>
-      <c r="B69" t="s">
-        <v>85</v>
-      </c>
-      <c r="C69" t="s">
-        <v>115</v>
-      </c>
-      <c r="D69" t="s">
-        <v>147</v>
-      </c>
-      <c r="E69" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920089</v>
-      </c>
-      <c r="B70" t="s">
-        <v>85</v>
-      </c>
-      <c r="C70" t="s">
-        <v>115</v>
-      </c>
-      <c r="D70" t="s">
-        <v>147</v>
-      </c>
-      <c r="E70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920089</v>
-      </c>
-      <c r="B71" t="s">
-        <v>85</v>
-      </c>
-      <c r="C71" t="s">
-        <v>115</v>
-      </c>
-      <c r="D71" t="s">
-        <v>147</v>
-      </c>
-      <c r="E71" t="s">
-        <v>8</v>
-      </c>
-      <c r="F71" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920092</v>
-      </c>
-      <c r="B72" t="s">
-        <v>86</v>
-      </c>
-      <c r="C72" t="s">
-        <v>116</v>
-      </c>
-      <c r="D72" t="s">
-        <v>148</v>
-      </c>
-      <c r="E72" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920092</v>
-      </c>
-      <c r="B73" t="s">
-        <v>86</v>
-      </c>
-      <c r="C73" t="s">
-        <v>116</v>
-      </c>
-      <c r="D73" t="s">
-        <v>148</v>
-      </c>
-      <c r="E73" t="s">
-        <v>5</v>
-      </c>
-      <c r="F73" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920092</v>
-      </c>
-      <c r="B74" t="s">
-        <v>86</v>
-      </c>
-      <c r="C74" t="s">
-        <v>116</v>
-      </c>
-      <c r="D74" t="s">
-        <v>148</v>
-      </c>
-      <c r="E74" t="s">
-        <v>10</v>
-      </c>
-      <c r="F74" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920092</v>
-      </c>
-      <c r="B75" t="s">
-        <v>86</v>
-      </c>
-      <c r="C75" t="s">
-        <v>116</v>
-      </c>
-      <c r="D75" t="s">
-        <v>148</v>
-      </c>
-      <c r="E75" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920093</v>
-      </c>
-      <c r="B76" t="s">
-        <v>87</v>
-      </c>
-      <c r="C76" t="s">
-        <v>91</v>
-      </c>
-      <c r="D76" t="s">
-        <v>149</v>
-      </c>
-      <c r="E76" t="s">
-        <v>5</v>
-      </c>
-      <c r="F76" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920093</v>
-      </c>
-      <c r="B77" t="s">
-        <v>87</v>
-      </c>
-      <c r="C77" t="s">
-        <v>91</v>
-      </c>
-      <c r="D77" t="s">
-        <v>149</v>
-      </c>
-      <c r="E77" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920093</v>
-      </c>
-      <c r="B78" t="s">
-        <v>87</v>
-      </c>
-      <c r="C78" t="s">
-        <v>91</v>
-      </c>
-      <c r="D78" t="s">
-        <v>149</v>
-      </c>
-      <c r="E78" t="s">
-        <v>8</v>
-      </c>
-      <c r="F78" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920094</v>
-      </c>
-      <c r="B79" t="s">
-        <v>88</v>
-      </c>
-      <c r="C79" t="s">
-        <v>117</v>
-      </c>
-      <c r="D79" t="s">
-        <v>150</v>
-      </c>
-      <c r="E79" t="s">
-        <v>6</v>
-      </c>
-      <c r="F79" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920094</v>
-      </c>
-      <c r="B80" t="s">
-        <v>88</v>
-      </c>
-      <c r="C80" t="s">
-        <v>117</v>
-      </c>
-      <c r="D80" t="s">
-        <v>150</v>
-      </c>
-      <c r="E80" t="s">
-        <v>5</v>
-      </c>
-      <c r="F80" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920094</v>
-      </c>
-      <c r="B81" t="s">
-        <v>88</v>
-      </c>
-      <c r="C81" t="s">
-        <v>117</v>
-      </c>
-      <c r="D81" t="s">
-        <v>150</v>
-      </c>
-      <c r="E81" t="s">
-        <v>10</v>
-      </c>
-      <c r="F81" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920094</v>
-      </c>
-      <c r="B82" t="s">
-        <v>88</v>
-      </c>
-      <c r="C82" t="s">
-        <v>117</v>
-      </c>
-      <c r="D82" t="s">
-        <v>150</v>
-      </c>
-      <c r="E82" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920096</v>
-      </c>
-      <c r="B83" t="s">
-        <v>88</v>
-      </c>
-      <c r="C83" t="s">
-        <v>118</v>
-      </c>
-      <c r="D83" t="s">
-        <v>151</v>
-      </c>
-      <c r="E83" t="s">
-        <v>7</v>
-      </c>
-      <c r="F83" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>21330051920096</v>
-      </c>
-      <c r="B84" t="s">
-        <v>88</v>
-      </c>
-      <c r="C84" t="s">
-        <v>118</v>
-      </c>
-      <c r="D84" t="s">
-        <v>151</v>
-      </c>
-      <c r="E84" t="s">
-        <v>5</v>
-      </c>
-      <c r="F84" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>21330051920096</v>
-      </c>
-      <c r="B85" t="s">
-        <v>88</v>
-      </c>
-      <c r="C85" t="s">
-        <v>118</v>
-      </c>
-      <c r="D85" t="s">
-        <v>151</v>
-      </c>
-      <c r="E85" t="s">
-        <v>10</v>
-      </c>
-      <c r="F85" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>21330051920096</v>
-      </c>
-      <c r="B86" t="s">
-        <v>88</v>
-      </c>
-      <c r="C86" t="s">
-        <v>118</v>
-      </c>
-      <c r="D86" t="s">
-        <v>151</v>
-      </c>
-      <c r="E86" t="s">
-        <v>8</v>
-      </c>
-      <c r="F86" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>21330051920097</v>
-      </c>
-      <c r="B87" t="s">
-        <v>89</v>
-      </c>
-      <c r="C87" t="s">
-        <v>119</v>
-      </c>
-      <c r="D87" t="s">
-        <v>152</v>
-      </c>
-      <c r="E87" t="s">
-        <v>7</v>
-      </c>
-      <c r="F87" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>21330051920097</v>
-      </c>
-      <c r="B88" t="s">
-        <v>89</v>
-      </c>
-      <c r="C88" t="s">
-        <v>119</v>
-      </c>
-      <c r="D88" t="s">
-        <v>152</v>
-      </c>
-      <c r="E88" t="s">
-        <v>5</v>
-      </c>
-      <c r="F88" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>21330051920097</v>
-      </c>
-      <c r="B89" t="s">
-        <v>89</v>
-      </c>
-      <c r="C89" t="s">
-        <v>119</v>
-      </c>
-      <c r="D89" t="s">
-        <v>152</v>
-      </c>
-      <c r="E89" t="s">
-        <v>10</v>
-      </c>
-      <c r="F89" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>21330051920097</v>
-      </c>
-      <c r="B90" t="s">
-        <v>89</v>
-      </c>
-      <c r="C90" t="s">
-        <v>119</v>
-      </c>
-      <c r="D90" t="s">
-        <v>152</v>
-      </c>
-      <c r="E90" t="s">
-        <v>8</v>
-      </c>
-      <c r="F90" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>18330051920296</v>
-      </c>
-      <c r="B91" t="s">
-        <v>88</v>
-      </c>
-      <c r="C91" t="s">
-        <v>120</v>
-      </c>
-      <c r="D91" t="s">
-        <v>153</v>
-      </c>
-      <c r="E91" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>18330051920296</v>
-      </c>
-      <c r="B92" t="s">
-        <v>88</v>
-      </c>
-      <c r="C92" t="s">
-        <v>120</v>
-      </c>
-      <c r="D92" t="s">
-        <v>153</v>
-      </c>
-      <c r="E92" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>21330051920098</v>
-      </c>
-      <c r="B93" t="s">
-        <v>90</v>
-      </c>
-      <c r="C93" t="s">
-        <v>84</v>
-      </c>
-      <c r="D93" t="s">
-        <v>154</v>
-      </c>
-      <c r="E93" t="s">
-        <v>7</v>
-      </c>
-      <c r="F93" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>21330051920098</v>
-      </c>
-      <c r="B94" t="s">
-        <v>90</v>
-      </c>
-      <c r="C94" t="s">
-        <v>84</v>
-      </c>
-      <c r="D94" t="s">
-        <v>154</v>
-      </c>
-      <c r="E94" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>21330051920098</v>
-      </c>
-      <c r="B95" t="s">
-        <v>90</v>
-      </c>
-      <c r="C95" t="s">
-        <v>84</v>
-      </c>
-      <c r="D95" t="s">
-        <v>154</v>
-      </c>
-      <c r="E95" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>21330051920098</v>
-      </c>
-      <c r="B96" t="s">
-        <v>90</v>
-      </c>
-      <c r="C96" t="s">
-        <v>84</v>
-      </c>
-      <c r="D96" t="s">
-        <v>154</v>
-      </c>
-      <c r="E96" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>21330051920099</v>
-      </c>
-      <c r="B97" t="s">
-        <v>90</v>
-      </c>
-      <c r="C97" t="s">
-        <v>88</v>
-      </c>
-      <c r="D97" t="s">
-        <v>155</v>
-      </c>
-      <c r="E97" t="s">
-        <v>7</v>
-      </c>
-      <c r="F97" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>21330051920099</v>
-      </c>
-      <c r="B98" t="s">
-        <v>90</v>
-      </c>
-      <c r="C98" t="s">
-        <v>88</v>
-      </c>
-      <c r="D98" t="s">
-        <v>155</v>
-      </c>
-      <c r="E98" t="s">
-        <v>5</v>
-      </c>
-      <c r="F98" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>21330051920099</v>
-      </c>
-      <c r="B99" t="s">
-        <v>90</v>
-      </c>
-      <c r="C99" t="s">
-        <v>88</v>
-      </c>
-      <c r="D99" t="s">
-        <v>155</v>
-      </c>
-      <c r="E99" t="s">
-        <v>10</v>
-      </c>
-      <c r="F99" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>21330051920099</v>
-      </c>
-      <c r="B100" t="s">
-        <v>90</v>
-      </c>
-      <c r="C100" t="s">
-        <v>88</v>
-      </c>
-      <c r="D100" t="s">
-        <v>155</v>
-      </c>
-      <c r="E100" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>21330051920100</v>
-      </c>
-      <c r="B101" t="s">
-        <v>91</v>
-      </c>
-      <c r="C101" t="s">
-        <v>121</v>
-      </c>
-      <c r="D101" t="s">
-        <v>156</v>
-      </c>
-      <c r="E101" t="s">
-        <v>7</v>
-      </c>
-      <c r="F101" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>21330051920100</v>
-      </c>
-      <c r="B102" t="s">
-        <v>91</v>
-      </c>
-      <c r="C102" t="s">
-        <v>121</v>
-      </c>
-      <c r="D102" t="s">
-        <v>156</v>
-      </c>
-      <c r="E102" t="s">
-        <v>5</v>
-      </c>
-      <c r="F102" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>21330051920100</v>
-      </c>
-      <c r="B103" t="s">
-        <v>91</v>
-      </c>
-      <c r="C103" t="s">
-        <v>121</v>
-      </c>
-      <c r="D103" t="s">
-        <v>156</v>
-      </c>
-      <c r="E103" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>21330051920100</v>
-      </c>
-      <c r="B104" t="s">
-        <v>91</v>
-      </c>
-      <c r="C104" t="s">
-        <v>121</v>
-      </c>
-      <c r="D104" t="s">
-        <v>156</v>
-      </c>
-      <c r="E104" t="s">
-        <v>8</v>
-      </c>
-      <c r="F104" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>21330051920101</v>
-      </c>
-      <c r="B105" t="s">
-        <v>92</v>
-      </c>
-      <c r="C105" t="s">
-        <v>90</v>
-      </c>
-      <c r="D105" t="s">
-        <v>157</v>
-      </c>
-      <c r="E105" t="s">
-        <v>5</v>
-      </c>
-      <c r="F105" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>21330051920101</v>
-      </c>
-      <c r="B106" t="s">
-        <v>92</v>
-      </c>
-      <c r="C106" t="s">
-        <v>90</v>
-      </c>
-      <c r="D106" t="s">
-        <v>157</v>
-      </c>
-      <c r="E106" t="s">
-        <v>10</v>
-      </c>
-      <c r="F106" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>21330051920101</v>
-      </c>
-      <c r="B107" t="s">
-        <v>92</v>
-      </c>
-      <c r="C107" t="s">
-        <v>90</v>
-      </c>
-      <c r="D107" t="s">
-        <v>157</v>
-      </c>
-      <c r="E107" t="s">
-        <v>8</v>
-      </c>
-      <c r="F107" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>21330051920383</v>
-      </c>
-      <c r="B108" t="s">
-        <v>93</v>
-      </c>
-      <c r="C108" t="s">
-        <v>94</v>
-      </c>
-      <c r="D108" t="s">
-        <v>158</v>
-      </c>
-      <c r="E108" t="s">
-        <v>7</v>
-      </c>
-      <c r="F108" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>21330051920383</v>
-      </c>
-      <c r="B109" t="s">
-        <v>93</v>
-      </c>
-      <c r="C109" t="s">
-        <v>94</v>
-      </c>
-      <c r="D109" t="s">
-        <v>158</v>
-      </c>
-      <c r="E109" t="s">
-        <v>5</v>
-      </c>
-      <c r="F109" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>21330051920383</v>
-      </c>
-      <c r="B110" t="s">
-        <v>93</v>
-      </c>
-      <c r="C110" t="s">
-        <v>94</v>
-      </c>
-      <c r="D110" t="s">
-        <v>158</v>
-      </c>
-      <c r="E110" t="s">
-        <v>10</v>
-      </c>
-      <c r="F110" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>21330051920383</v>
-      </c>
-      <c r="B111" t="s">
-        <v>93</v>
-      </c>
-      <c r="C111" t="s">
-        <v>94</v>
-      </c>
-      <c r="D111" t="s">
-        <v>158</v>
-      </c>
-      <c r="E111" t="s">
-        <v>8</v>
-      </c>
-      <c r="F111" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>21330051920102</v>
-      </c>
-      <c r="B112" t="s">
-        <v>94</v>
-      </c>
-      <c r="C112" t="s">
-        <v>75</v>
-      </c>
-      <c r="D112" t="s">
-        <v>159</v>
-      </c>
-      <c r="E112" t="s">
-        <v>5</v>
-      </c>
-      <c r="F112" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>21330051920102</v>
-      </c>
-      <c r="B113" t="s">
-        <v>94</v>
-      </c>
-      <c r="C113" t="s">
-        <v>75</v>
-      </c>
-      <c r="D113" t="s">
-        <v>159</v>
-      </c>
-      <c r="E113" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>21330051920102</v>
-      </c>
-      <c r="B114" t="s">
-        <v>94</v>
-      </c>
-      <c r="C114" t="s">
-        <v>75</v>
-      </c>
-      <c r="D114" t="s">
-        <v>159</v>
-      </c>
-      <c r="E114" t="s">
-        <v>8</v>
-      </c>
-      <c r="F114" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>21330051920103</v>
-      </c>
-      <c r="B115" t="s">
-        <v>95</v>
-      </c>
-      <c r="C115" t="s">
-        <v>84</v>
-      </c>
-      <c r="D115" t="s">
-        <v>160</v>
-      </c>
-      <c r="E115" t="s">
-        <v>7</v>
-      </c>
-      <c r="F115" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>21330051920103</v>
-      </c>
-      <c r="B116" t="s">
-        <v>95</v>
-      </c>
-      <c r="C116" t="s">
-        <v>84</v>
-      </c>
-      <c r="D116" t="s">
-        <v>160</v>
-      </c>
-      <c r="E116" t="s">
-        <v>5</v>
-      </c>
-      <c r="F116" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>21330051920103</v>
-      </c>
-      <c r="B117" t="s">
-        <v>95</v>
-      </c>
-      <c r="C117" t="s">
-        <v>84</v>
-      </c>
-      <c r="D117" t="s">
-        <v>160</v>
-      </c>
-      <c r="E117" t="s">
-        <v>10</v>
-      </c>
-      <c r="F117" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>21330051920103</v>
-      </c>
-      <c r="B118" t="s">
-        <v>95</v>
-      </c>
-      <c r="C118" t="s">
-        <v>84</v>
-      </c>
-      <c r="D118" t="s">
-        <v>160</v>
-      </c>
-      <c r="E118" t="s">
-        <v>8</v>
-      </c>
-      <c r="F118" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>21330051920104</v>
-      </c>
-      <c r="B119" t="s">
-        <v>96</v>
-      </c>
-      <c r="C119" t="s">
-        <v>122</v>
-      </c>
-      <c r="D119" t="s">
-        <v>161</v>
-      </c>
-      <c r="E119" t="s">
-        <v>7</v>
-      </c>
-      <c r="F119" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>21330051920104</v>
-      </c>
-      <c r="B120" t="s">
-        <v>96</v>
-      </c>
-      <c r="C120" t="s">
-        <v>122</v>
-      </c>
-      <c r="D120" t="s">
-        <v>161</v>
-      </c>
-      <c r="E120" t="s">
-        <v>5</v>
-      </c>
-      <c r="F120" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>21330051920104</v>
-      </c>
-      <c r="B121" t="s">
-        <v>96</v>
-      </c>
-      <c r="C121" t="s">
-        <v>122</v>
-      </c>
-      <c r="D121" t="s">
-        <v>161</v>
-      </c>
-      <c r="E121" t="s">
-        <v>10</v>
-      </c>
-      <c r="F121" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>21330051920104</v>
-      </c>
-      <c r="B122" t="s">
-        <v>96</v>
-      </c>
-      <c r="C122" t="s">
-        <v>122</v>
-      </c>
-      <c r="D122" t="s">
-        <v>161</v>
-      </c>
-      <c r="E122" t="s">
-        <v>8</v>
-      </c>
-      <c r="F122" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>21330051920105</v>
-      </c>
-      <c r="B123" t="s">
-        <v>97</v>
-      </c>
-      <c r="C123" t="s">
-        <v>123</v>
-      </c>
-      <c r="D123" t="s">
-        <v>162</v>
-      </c>
-      <c r="E123" t="s">
-        <v>5</v>
-      </c>
-      <c r="F123" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>21330051920105</v>
-      </c>
-      <c r="B124" t="s">
-        <v>97</v>
-      </c>
-      <c r="C124" t="s">
-        <v>123</v>
-      </c>
-      <c r="D124" t="s">
-        <v>162</v>
-      </c>
-      <c r="E124" t="s">
-        <v>10</v>
-      </c>
-      <c r="F124" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>21330051920105</v>
-      </c>
-      <c r="B125" t="s">
-        <v>97</v>
-      </c>
-      <c r="C125" t="s">
-        <v>123</v>
-      </c>
-      <c r="D125" t="s">
-        <v>162</v>
-      </c>
-      <c r="E125" t="s">
-        <v>8</v>
-      </c>
-      <c r="F125" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>21330051920106</v>
-      </c>
-      <c r="B126" t="s">
-        <v>98</v>
-      </c>
-      <c r="C126" t="s">
-        <v>124</v>
-      </c>
-      <c r="D126" t="s">
-        <v>163</v>
-      </c>
-      <c r="E126" t="s">
-        <v>5</v>
-      </c>
-      <c r="F126" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>21330051920106</v>
-      </c>
-      <c r="B127" t="s">
-        <v>98</v>
-      </c>
-      <c r="C127" t="s">
-        <v>124</v>
-      </c>
-      <c r="D127" t="s">
-        <v>163</v>
-      </c>
-      <c r="E127" t="s">
-        <v>10</v>
-      </c>
-      <c r="F127" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>21330051920106</v>
-      </c>
-      <c r="B128" t="s">
-        <v>98</v>
-      </c>
-      <c r="C128" t="s">
-        <v>124</v>
-      </c>
-      <c r="D128" t="s">
-        <v>163</v>
-      </c>
-      <c r="E128" t="s">
-        <v>8</v>
-      </c>
-      <c r="F128" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>21330051920107</v>
-      </c>
-      <c r="B129" t="s">
-        <v>99</v>
-      </c>
-      <c r="C129" t="s">
-        <v>125</v>
-      </c>
-      <c r="D129" t="s">
-        <v>164</v>
-      </c>
-      <c r="E129" t="s">
-        <v>7</v>
-      </c>
-      <c r="F129" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>21330051920107</v>
-      </c>
-      <c r="B130" t="s">
-        <v>99</v>
-      </c>
-      <c r="C130" t="s">
-        <v>125</v>
-      </c>
-      <c r="D130" t="s">
-        <v>164</v>
-      </c>
-      <c r="E130" t="s">
-        <v>5</v>
-      </c>
-      <c r="F130" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
-        <v>21330051920107</v>
-      </c>
-      <c r="B131" t="s">
-        <v>99</v>
-      </c>
-      <c r="C131" t="s">
-        <v>125</v>
-      </c>
-      <c r="D131" t="s">
-        <v>164</v>
-      </c>
-      <c r="E131" t="s">
-        <v>10</v>
-      </c>
-      <c r="F131" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132">
-        <v>21330051920107</v>
-      </c>
-      <c r="B132" t="s">
-        <v>99</v>
-      </c>
-      <c r="C132" t="s">
-        <v>125</v>
-      </c>
-      <c r="D132" t="s">
-        <v>164</v>
-      </c>
-      <c r="E132" t="s">
-        <v>8</v>
-      </c>
-      <c r="F132" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>18330051920309</v>
-      </c>
-      <c r="B133" t="s">
-        <v>100</v>
-      </c>
-      <c r="C133" t="s">
-        <v>126</v>
-      </c>
-      <c r="D133" t="s">
-        <v>165</v>
-      </c>
-      <c r="E133" t="s">
-        <v>10</v>
-      </c>
-      <c r="F133" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134">
-        <v>18330051920309</v>
-      </c>
-      <c r="B134" t="s">
-        <v>100</v>
-      </c>
-      <c r="C134" t="s">
-        <v>126</v>
-      </c>
-      <c r="D134" t="s">
-        <v>165</v>
-      </c>
-      <c r="E134" t="s">
-        <v>8</v>
-      </c>
-      <c r="F134" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135">
-        <v>21330051920109</v>
-      </c>
-      <c r="B135" t="s">
-        <v>101</v>
-      </c>
-      <c r="C135" t="s">
-        <v>127</v>
-      </c>
-      <c r="D135" t="s">
-        <v>166</v>
-      </c>
-      <c r="E135" t="s">
-        <v>7</v>
-      </c>
-      <c r="F135" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136">
-        <v>21330051920109</v>
-      </c>
-      <c r="B136" t="s">
-        <v>101</v>
-      </c>
-      <c r="C136" t="s">
-        <v>127</v>
-      </c>
-      <c r="D136" t="s">
-        <v>166</v>
-      </c>
-      <c r="E136" t="s">
-        <v>6</v>
-      </c>
-      <c r="F136" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137">
-        <v>21330051920109</v>
-      </c>
-      <c r="B137" t="s">
-        <v>101</v>
-      </c>
-      <c r="C137" t="s">
-        <v>127</v>
-      </c>
-      <c r="D137" t="s">
-        <v>166</v>
-      </c>
-      <c r="E137" t="s">
-        <v>5</v>
-      </c>
-      <c r="F137" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138">
-        <v>21330051920109</v>
-      </c>
-      <c r="B138" t="s">
-        <v>101</v>
-      </c>
-      <c r="C138" t="s">
-        <v>127</v>
-      </c>
-      <c r="D138" t="s">
-        <v>166</v>
-      </c>
-      <c r="E138" t="s">
-        <v>10</v>
-      </c>
-      <c r="F138" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139">
-        <v>21330051920109</v>
-      </c>
-      <c r="B139" t="s">
-        <v>101</v>
-      </c>
-      <c r="C139" t="s">
-        <v>127</v>
-      </c>
-      <c r="D139" t="s">
-        <v>166</v>
-      </c>
-      <c r="E139" t="s">
-        <v>8</v>
-      </c>
-      <c r="F139" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140">
-        <v>21330051920387</v>
-      </c>
-      <c r="B140" t="s">
-        <v>102</v>
-      </c>
-      <c r="C140" t="s">
-        <v>128</v>
-      </c>
-      <c r="D140" t="s">
-        <v>167</v>
-      </c>
-      <c r="E140" t="s">
-        <v>5</v>
-      </c>
-      <c r="F140" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141">
-        <v>21330051920387</v>
-      </c>
-      <c r="B141" t="s">
-        <v>102</v>
-      </c>
-      <c r="C141" t="s">
-        <v>128</v>
-      </c>
-      <c r="D141" t="s">
-        <v>167</v>
-      </c>
-      <c r="E141" t="s">
-        <v>10</v>
-      </c>
-      <c r="F141" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142">
-        <v>21330051920387</v>
-      </c>
-      <c r="B142" t="s">
-        <v>102</v>
-      </c>
-      <c r="C142" t="s">
-        <v>128</v>
-      </c>
-      <c r="D142" t="s">
-        <v>167</v>
-      </c>
-      <c r="E142" t="s">
-        <v>8</v>
-      </c>
-      <c r="F142" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -7050,50 +5159,50 @@
         <v>21330051920108</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920109</v>
+        <v>21330051920107</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920072</v>
+        <v>21330051920109</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7104,13 +5213,13 @@
         <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7118,16 +5227,16 @@
         <v>21330051920076</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7135,16 +5244,16 @@
         <v>21330051920077</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7152,16 +5261,16 @@
         <v>21330051920078</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7169,560 +5278,560 @@
         <v>21330051920080</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920082</v>
+        <v>21330051920092</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920085</v>
+        <v>21330051920094</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920302</v>
+        <v>21330051920097</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920092</v>
+        <v>21330051920098</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920094</v>
+        <v>21330051920100</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920096</v>
+        <v>21330051920102</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920097</v>
+        <v>21330051920103</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920098</v>
+        <v>21330051920104</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920099</v>
+        <v>21330051920071</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920100</v>
+        <v>21330051920072</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920383</v>
+        <v>21330051920082</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920103</v>
+        <v>21330051920085</v>
       </c>
       <c r="B21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" t="s">
         <v>95</v>
       </c>
-      <c r="C21" t="s">
-        <v>84</v>
-      </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>118</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920104</v>
+        <v>21330051920086</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>161</v>
+        <v>119</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920107</v>
+        <v>20330051920302</v>
       </c>
       <c r="B23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" t="s">
         <v>99</v>
       </c>
-      <c r="C23" t="s">
-        <v>125</v>
-      </c>
       <c r="D23" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920071</v>
+        <v>21330051920096</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920074</v>
+        <v>18330051920296</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920075</v>
+        <v>21330051920099</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920079</v>
+        <v>21330051920383</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920081</v>
+        <v>21330051920074</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920083</v>
+        <v>20330051920378</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920084</v>
+        <v>21330051920075</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920086</v>
+        <v>21330051920079</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920089</v>
+        <v>21330051920081</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="D32" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920093</v>
+        <v>21330051920083</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920101</v>
+        <v>21330051920084</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>149</v>
       </c>
       <c r="D34" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920102</v>
+        <v>21330051920089</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920105</v>
+        <v>21330051920093</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
         <v>162</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920106</v>
+        <v>21330051920101</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
         <v>163</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920387</v>
+        <v>21330051920105</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="C38" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D38" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>20330051920378</v>
+        <v>21330051920106</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>141</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="D39" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>18330051920296</v>
+        <v>18330051920309</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="C40" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="D40" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>18330051920309</v>
+        <v>21330051920387</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="C41" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="D41" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7732,7 +5841,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7764,22 +5873,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920378</v>
+        <v>21330051920357</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -7787,22 +5896,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920378</v>
+        <v>21330051920357</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -7810,22 +5919,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>18330051920296</v>
+        <v>21330051920076</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -7833,22 +5942,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>18330051920296</v>
+        <v>21330051920076</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -7856,22 +5965,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>18330051920309</v>
+        <v>21330051920077</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -7879,24 +5988,668 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>18330051920309</v>
+        <v>21330051920077</v>
       </c>
       <c r="B7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920080</v>
+      </c>
+      <c r="B8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920080</v>
+      </c>
+      <c r="B9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920092</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
         <v>100</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D10" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920092</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920094</v>
+      </c>
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920094</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920097</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920097</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920098</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
         <v>126</v>
       </c>
-      <c r="D7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
         <v>62</v>
       </c>
-      <c r="G7">
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920098</v>
+      </c>
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920100</v>
+      </c>
+      <c r="B18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920100</v>
+      </c>
+      <c r="B19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920102</v>
+      </c>
+      <c r="B21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920103</v>
+      </c>
+      <c r="B22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920103</v>
+      </c>
+      <c r="B23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" t="s">
+        <v>131</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920104</v>
+      </c>
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920104</v>
+      </c>
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" t="s">
+        <v>132</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920071</v>
+      </c>
+      <c r="B26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" t="s">
+        <v>62</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>21330051920072</v>
+      </c>
+      <c r="B27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>21330051920082</v>
+      </c>
+      <c r="B28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" t="s">
+        <v>117</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>21330051920085</v>
+      </c>
+      <c r="B29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" t="s">
+        <v>64</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>21330051920086</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>20330051920302</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" t="s">
+        <v>120</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>61</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>21330051920096</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" t="s">
+        <v>123</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>18330051920296</v>
+      </c>
+      <c r="B33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>63</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>21330051920099</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" t="s">
+        <v>127</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>21330051920383</v>
+      </c>
+      <c r="B35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>61</v>
+      </c>
+      <c r="G35">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ALCV - Estadisticos 20212.xlsx
+++ b/grupos/2ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="168">
   <si>
     <t>Materia</t>
   </si>
@@ -326,187 +326,187 @@
     <t>BRAVO</t>
   </si>
   <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>KATHIA</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>KATHIA</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>MARYFER</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>CRISTAL YOSELIN</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>BERENICE</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>REGINA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
   </si>
   <si>
     <t>DIANA IVONNE</t>
   </si>
   <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>INGRID AMERICA</t>
+    <t>FATIMA MARILYN</t>
+  </si>
+  <si>
+    <t>ITZEL ABIGAIL</t>
   </si>
   <si>
     <t>JAIME</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>CRISTAL YOSELIN</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
   </si>
   <si>
     <t>CITLALI ESPERANZA</t>
@@ -1028,7 +1028,7 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -1105,7 +1105,7 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1141,7 +1141,7 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1295,7 +1295,7 @@
         <v>8</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1442,7 +1442,7 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1478,7 +1478,7 @@
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1501,7 +1501,7 @@
         <v>-1</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>-1</v>
@@ -1555,7 +1555,7 @@
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1596,7 +1596,7 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1632,7 +1632,7 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1750,7 +1750,7 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1904,7 +1904,7 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -1940,7 +1940,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -1981,7 +1981,7 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -2017,7 +2017,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2058,7 +2058,7 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -2094,7 +2094,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -2212,7 +2212,7 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2248,7 +2248,7 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2271,7 +2271,7 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>10</v>
@@ -2325,7 +2325,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2366,7 +2366,7 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2402,7 +2402,7 @@
         <v>7</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2508,7 +2508,7 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2544,7 +2544,7 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -2662,7 +2662,7 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2739,7 +2739,7 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2775,7 +2775,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>-1</v>
@@ -2798,7 +2798,7 @@
         <v>7</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>10</v>
@@ -2852,7 +2852,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>10</v>
@@ -2878,7 +2878,7 @@
         <v>8</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E29">
         <v>9</v>
@@ -2893,7 +2893,7 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -2929,10 +2929,10 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -3076,7 +3076,7 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -3112,7 +3112,7 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>-1</v>
@@ -3153,7 +3153,7 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -3189,7 +3189,7 @@
         <v>-1</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>-1</v>
@@ -3230,7 +3230,7 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
         <v>-1</v>
@@ -3615,7 +3615,7 @@
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
         <v>-1</v>
@@ -3651,7 +3651,7 @@
         <v>8</v>
       </c>
       <c r="U39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V39">
         <v>10</v>
@@ -3780,7 +3780,7 @@
         <v>-1</v>
       </c>
       <c r="C42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D42">
         <v>-1</v>
@@ -3834,7 +3834,7 @@
         <v>-1</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V42">
         <v>-1</v>
@@ -3988,25 +3988,25 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>45.95</v>
+        <v>48.65</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J2">
-        <v>54.05</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4087,22 +4087,22 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>88.89</v>
       </c>
       <c r="G5">
+        <v>11.11</v>
+      </c>
+      <c r="H5">
+        <v>7.8</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="H5">
-        <v>7.6</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
       <c r="J5">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4176,7 +4176,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4214,7 +4214,7 @@
         <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4234,7 +4234,7 @@
         <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4254,7 +4254,7 @@
         <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4274,7 +4274,7 @@
         <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -4294,7 +4294,7 @@
         <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4314,13 +4314,13 @@
         <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4334,33 +4334,33 @@
         <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920108</v>
+        <v>21330051920076</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
         <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4374,33 +4374,33 @@
         <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920076</v>
+        <v>21330051920077</v>
       </c>
       <c r="B11" t="s">
         <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
         <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4414,33 +4414,33 @@
         <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920077</v>
+        <v>21330051920078</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
         <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4454,33 +4454,33 @@
         <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920078</v>
+        <v>21330051920080</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4494,184 +4494,184 @@
         <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920080</v>
+        <v>21330051920082</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920082</v>
+        <v>21330051920086</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
         <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920085</v>
+        <v>20330051920302</v>
       </c>
       <c r="B19" t="s">
         <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
         <v>118</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920086</v>
+        <v>21330051920092</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
         <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920302</v>
+        <v>21330051920092</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920092</v>
+        <v>21330051920094</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920092</v>
+        <v>21330051920097</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
         <v>121</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920094</v>
+        <v>21330051920097</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920094</v>
+        <v>18330051920296</v>
       </c>
       <c r="B25" t="s">
         <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
         <v>122</v>
@@ -4685,13 +4685,13 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920096</v>
+        <v>21330051920098</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
         <v>123</v>
@@ -4705,50 +4705,50 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920097</v>
+        <v>21330051920098</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920097</v>
+        <v>21330051920099</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="D28" t="s">
         <v>124</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>18330051920296</v>
+        <v>21330051920100</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
         <v>104</v>
@@ -4757,184 +4757,184 @@
         <v>125</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920098</v>
+        <v>21330051920100</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="D30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920098</v>
+        <v>21330051920383</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D31" t="s">
         <v>126</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920099</v>
+        <v>21330051920102</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
         <v>127</v>
       </c>
       <c r="E32" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920100</v>
+        <v>21330051920102</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
         <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920100</v>
+        <v>21330051920103</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
         <v>128</v>
       </c>
       <c r="E34" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920383</v>
+        <v>21330051920103</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E35" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920102</v>
+        <v>21330051920104</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
         <v>106</v>
       </c>
       <c r="D36" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E36" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920102</v>
+        <v>21330051920104</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
         <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920103</v>
+        <v>21330051920107</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="D38" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E38" t="s">
         <v>7</v>
@@ -4945,16 +4945,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920103</v>
+        <v>21330051920107</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="D39" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E39" t="s">
         <v>5</v>
@@ -4965,161 +4965,61 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>21330051920104</v>
+        <v>21330051920107</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
         <v>107</v>
       </c>
       <c r="D40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920104</v>
+        <v>21330051920109</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D41" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E41" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920107</v>
+        <v>21330051920109</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C42" t="s">
         <v>108</v>
       </c>
       <c r="D42" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E42" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F42" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920107</v>
-      </c>
-      <c r="B43" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" t="s">
-        <v>108</v>
-      </c>
-      <c r="D43" t="s">
-        <v>133</v>
-      </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920107</v>
-      </c>
-      <c r="B44" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" t="s">
-        <v>108</v>
-      </c>
-      <c r="D44" t="s">
-        <v>133</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920109</v>
-      </c>
-      <c r="B45" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" t="s">
-        <v>109</v>
-      </c>
-      <c r="D45" t="s">
-        <v>134</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920109</v>
-      </c>
-      <c r="B46" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" t="s">
-        <v>109</v>
-      </c>
-      <c r="D46" t="s">
-        <v>134</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920109</v>
-      </c>
-      <c r="B47" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" t="s">
-        <v>109</v>
-      </c>
-      <c r="D47" t="s">
-        <v>134</v>
-      </c>
-      <c r="E47" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
         <v>62</v>
       </c>
     </row>
@@ -5165,10 +5065,10 @@
         <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5179,10 +5079,10 @@
         <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -5190,33 +5090,33 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920109</v>
+        <v>21330051920357</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920357</v>
+        <v>21330051920076</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -5224,13 +5124,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920076</v>
+        <v>21330051920077</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
         <v>114</v>
@@ -5241,13 +5141,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920077</v>
+        <v>21330051920078</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
         <v>115</v>
@@ -5258,16 +5158,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920078</v>
+        <v>21330051920080</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -5275,16 +5175,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920080</v>
+        <v>21330051920092</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -5292,13 +5192,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920092</v>
+        <v>21330051920097</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
         <v>121</v>
@@ -5309,16 +5209,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920094</v>
+        <v>21330051920098</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -5326,16 +5226,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920097</v>
+        <v>21330051920100</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -5343,16 +5243,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920098</v>
+        <v>21330051920102</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -5360,13 +5260,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920100</v>
+        <v>21330051920103</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
         <v>128</v>
@@ -5377,16 +5277,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920102</v>
+        <v>21330051920104</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
         <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -5394,13 +5294,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920103</v>
+        <v>21330051920109</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
         <v>131</v>
@@ -5411,30 +5311,30 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920104</v>
+        <v>21330051920071</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920071</v>
+        <v>21330051920072</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
         <v>110</v>
@@ -5445,16 +5345,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920072</v>
+        <v>21330051920082</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -5462,13 +5362,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920082</v>
+        <v>21330051920086</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
         <v>117</v>
@@ -5479,13 +5379,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920085</v>
+        <v>20330051920302</v>
       </c>
       <c r="B21" t="s">
         <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
         <v>118</v>
@@ -5496,16 +5396,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920086</v>
+        <v>21330051920094</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -5513,16 +5413,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920302</v>
+        <v>18330051920296</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -5530,16 +5430,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920096</v>
+        <v>21330051920099</v>
       </c>
       <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
         <v>81</v>
       </c>
-      <c r="C24" t="s">
-        <v>102</v>
-      </c>
       <c r="D24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -5547,16 +5447,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>18330051920296</v>
+        <v>21330051920383</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -5564,47 +5464,47 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920099</v>
+        <v>21330051920074</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920383</v>
+        <v>20330051920378</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920074</v>
+        <v>21330051920075</v>
       </c>
       <c r="B28" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D28" t="s">
         <v>154</v>
@@ -5615,13 +5515,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920378</v>
+        <v>21330051920079</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D29" t="s">
         <v>155</v>
@@ -5632,13 +5532,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920075</v>
+        <v>21330051920081</v>
       </c>
       <c r="B30" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D30" t="s">
         <v>156</v>
@@ -5649,13 +5549,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920079</v>
+        <v>21330051920083</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
         <v>157</v>
@@ -5666,13 +5566,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920081</v>
+        <v>21330051920084</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D32" t="s">
         <v>158</v>
@@ -5683,13 +5583,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920083</v>
+        <v>21330051920085</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="D33" t="s">
         <v>159</v>
@@ -5700,13 +5600,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920084</v>
+        <v>21330051920089</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="C34" t="s">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
         <v>160</v>
@@ -5717,13 +5617,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920089</v>
+        <v>21330051920093</v>
       </c>
       <c r="B35" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D35" t="s">
         <v>161</v>
@@ -5734,13 +5634,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920093</v>
+        <v>21330051920096</v>
       </c>
       <c r="B36" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="D36" t="s">
         <v>162</v>
@@ -5754,7 +5654,7 @@
         <v>21330051920101</v>
       </c>
       <c r="B37" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s">
         <v>83</v>
@@ -5771,10 +5671,10 @@
         <v>21330051920105</v>
       </c>
       <c r="B38" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D38" t="s">
         <v>164</v>
@@ -5788,10 +5688,10 @@
         <v>21330051920106</v>
       </c>
       <c r="B39" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D39" t="s">
         <v>165</v>
@@ -5805,10 +5705,10 @@
         <v>18330051920309</v>
       </c>
       <c r="B40" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C40" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D40" t="s">
         <v>166</v>
@@ -5822,10 +5722,10 @@
         <v>21330051920387</v>
       </c>
       <c r="B41" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D41" t="s">
         <v>167</v>
@@ -5841,7 +5741,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5882,7 +5782,7 @@
         <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5905,7 +5805,7 @@
         <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -5928,7 +5828,7 @@
         <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5951,7 +5851,7 @@
         <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -5974,7 +5874,7 @@
         <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5997,7 +5897,7 @@
         <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -6020,7 +5920,7 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -6043,7 +5943,7 @@
         <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6066,7 +5966,7 @@
         <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -6089,7 +5989,7 @@
         <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -6112,7 +6012,7 @@
         <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -6121,7 +6021,7 @@
         <v>64</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -6135,7 +6035,7 @@
         <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -6155,10 +6055,10 @@
         <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -6178,10 +6078,10 @@
         <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -6204,7 +6104,7 @@
         <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -6227,7 +6127,7 @@
         <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -6247,10 +6147,10 @@
         <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
@@ -6270,10 +6170,10 @@
         <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -6293,10 +6193,10 @@
         <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
         <v>5</v>
@@ -6316,10 +6216,10 @@
         <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -6342,7 +6242,7 @@
         <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
@@ -6365,7 +6265,7 @@
         <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -6385,10 +6285,10 @@
         <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E24" t="s">
         <v>5</v>
@@ -6408,10 +6308,10 @@
         <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E25" t="s">
         <v>7</v>
@@ -6434,7 +6334,7 @@
         <v>91</v>
       </c>
       <c r="D26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
@@ -6457,7 +6357,7 @@
         <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -6480,7 +6380,7 @@
         <v>97</v>
       </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
@@ -6503,7 +6403,7 @@
         <v>95</v>
       </c>
       <c r="D29" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="E29" t="s">
         <v>6</v>
@@ -6512,7 +6412,7 @@
         <v>64</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -6526,7 +6426,7 @@
         <v>98</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -6549,7 +6449,7 @@
         <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E31" t="s">
         <v>7</v>
@@ -6563,22 +6463,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920096</v>
+        <v>18330051920296</v>
       </c>
       <c r="B32" t="s">
         <v>81</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D32" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G32">
         <v>-1</v>
@@ -6586,22 +6486,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>18330051920296</v>
+        <v>21330051920099</v>
       </c>
       <c r="B33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" t="s">
         <v>81</v>
       </c>
-      <c r="C33" t="s">
-        <v>104</v>
-      </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G33">
         <v>-1</v>
@@ -6609,16 +6509,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920099</v>
+        <v>21330051920383</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E34" t="s">
         <v>7</v>
@@ -6627,29 +6527,6 @@
         <v>61</v>
       </c>
       <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920383</v>
-      </c>
-      <c r="B35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" t="s">
-        <v>86</v>
-      </c>
-      <c r="D35" t="s">
-        <v>129</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>61</v>
-      </c>
-      <c r="G35">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ALCV - Estadisticos 20212.xlsx
+++ b/grupos/2ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="168">
   <si>
     <t>Materia</t>
   </si>
@@ -203,21 +203,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
@@ -233,52 +233,130 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CHACÓN</t>
+  </si>
+  <si>
+    <t>CABALLERO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>KATHIA</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>CHACÓN</t>
-  </si>
-  <si>
-    <t>CABALLERO</t>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
   </si>
   <si>
     <t>ELPIDIO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>OLIVARES</t>
   </si>
   <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>PELLICO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>SANJUAN</t>
@@ -287,31 +365,37 @@
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>BRETON</t>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
   </si>
   <si>
     <t>RIVERA</t>
@@ -326,34 +410,40 @@
     <t>BRAVO</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>QUIÑONES</t>
   </si>
   <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>VERA</t>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
   </si>
   <si>
     <t>ABIGAIL</t>
   </si>
   <si>
-    <t>KATHIA</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
+    <t>CRISTAL YOSELIN</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
   </si>
   <si>
     <t>MARYFER</t>
@@ -362,13 +452,22 @@
     <t>YARED</t>
   </si>
   <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
     <t>MIROSLAVA</t>
   </si>
   <si>
-    <t>VANESSA AMAIRANY</t>
+    <t>BERENICE</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>REGINA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
   </si>
   <si>
     <t>FATIMA</t>
@@ -377,28 +476,31 @@
     <t>JOSE ISAAC</t>
   </si>
   <si>
+    <t>FATIMA MARILYN</t>
+  </si>
+  <si>
     <t>JOSE JULIAN</t>
   </si>
   <si>
+    <t>ITZEL ABIGAIL</t>
+  </si>
+  <si>
     <t>INGRID AMERICA</t>
   </si>
   <si>
+    <t>JAIME</t>
+  </si>
+  <si>
     <t>JAZMIN</t>
   </si>
   <si>
     <t>MONICA</t>
   </si>
   <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
     <t>LUIS REY</t>
   </si>
   <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
+    <t>CITLALI ESPERANZA</t>
   </si>
   <si>
     <t>ANGEL DAVID</t>
@@ -408,108 +510,6 @@
   </si>
   <si>
     <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>CRISTAL YOSELIN</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
   </si>
   <si>
     <t>ANGELES</t>
@@ -1007,7 +1007,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>7</v>
@@ -1025,22 +1025,22 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1061,19 +1061,19 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>7</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>9</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -1084,7 +1084,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>7</v>
@@ -1102,7 +1102,7 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>8</v>
@@ -1138,7 +1138,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -1179,7 +1179,7 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1215,7 +1215,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>7</v>
@@ -1256,22 +1256,22 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1321,7 +1321,7 @@
         <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1333,7 +1333,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1362,7 +1362,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -1371,13 +1371,13 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1398,7 +1398,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1410,7 +1410,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1421,13 +1421,13 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>7</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -1439,22 +1439,22 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1475,22 +1475,22 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>8</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>8</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1498,13 +1498,13 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>5</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <v>8</v>
@@ -1513,25 +1513,25 @@
         <v>5</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1552,13 +1552,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1567,7 +1567,7 @@
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1593,7 +1593,7 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>8</v>
@@ -1602,13 +1602,13 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1638,7 +1638,7 @@
         <v>10</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -1652,13 +1652,13 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>7</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E13">
         <v>7</v>
@@ -1670,22 +1670,22 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1706,22 +1706,22 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1729,7 +1729,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>9</v>
@@ -1747,7 +1747,7 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>9</v>
@@ -1756,7 +1756,7 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1783,7 +1783,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>9</v>
@@ -1792,7 +1792,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1806,13 +1806,13 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>6</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E15">
         <v>7</v>
@@ -1824,22 +1824,22 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1860,22 +1860,22 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1901,22 +1901,22 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1966,7 +1966,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E17">
         <v>7</v>
@@ -1975,25 +1975,25 @@
         <v>7</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2020,16 +2020,16 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2055,22 +2055,22 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2091,19 +2091,19 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>10</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>9</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -2132,7 +2132,7 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2141,13 +2141,13 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2168,7 +2168,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2177,7 +2177,7 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2209,22 +2209,22 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2245,7 +2245,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>9</v>
@@ -2254,10 +2254,10 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2286,22 +2286,22 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2322,10 +2322,10 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2334,10 +2334,10 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2360,25 +2360,25 @@
         <v>9</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2399,13 +2399,13 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>9</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2414,7 +2414,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2425,7 +2425,7 @@
         <v>6</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E23">
         <v>7</v>
@@ -2437,19 +2437,19 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2470,7 +2470,7 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2505,22 +2505,22 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2541,7 +2541,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2550,13 +2550,13 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2564,13 +2564,13 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C25">
         <v>10</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>10</v>
@@ -2582,22 +2582,22 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2618,13 +2618,13 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2633,7 +2633,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2659,22 +2659,22 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2695,7 +2695,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -2710,7 +2710,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2724,7 +2724,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>9</v>
@@ -2733,19 +2733,19 @@
         <v>6</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -2778,16 +2778,16 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2810,10 +2810,10 @@
         <v>8</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>5</v>
@@ -2864,7 +2864,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2890,22 +2890,22 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2926,19 +2926,19 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>9</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2952,13 +2952,13 @@
         <v>7</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -2967,10 +2967,10 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2978,7 +2978,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>7</v>
@@ -2996,16 +2996,16 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3032,7 +3032,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U31">
         <v>7</v>
@@ -3061,7 +3061,7 @@
         <v>7</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E32">
         <v>8</v>
@@ -3073,22 +3073,22 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3109,13 +3109,13 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>8</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>8</v>
@@ -3132,7 +3132,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C33">
         <v>7</v>
@@ -3150,7 +3150,7 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -3159,13 +3159,13 @@
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3186,7 +3186,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>8</v>
@@ -3195,13 +3195,13 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3227,22 +3227,22 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>7</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3269,13 +3269,13 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3304,22 +3304,22 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J35">
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3355,7 +3355,7 @@
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3363,7 +3363,7 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>7</v>
@@ -3378,25 +3378,25 @@
         <v>8</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3417,13 +3417,13 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U36">
         <v>7</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3432,7 +3432,7 @@
         <v>8</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3440,13 +3440,13 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>10</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E37">
         <v>7</v>
@@ -3458,16 +3458,16 @@
         <v>7</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
         <v>-1</v>
@@ -3494,16 +3494,16 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U37">
         <v>10</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X37">
         <v>6</v>
@@ -3535,13 +3535,13 @@
         <v>8</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I38">
         <v>6</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -3550,7 +3550,7 @@
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3571,7 +3571,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U38">
         <v>7</v>
@@ -3612,22 +3612,22 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
         <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3648,13 +3648,13 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U39">
         <v>9</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W39">
         <v>10</v>
@@ -3671,7 +3671,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>7</v>
@@ -3686,19 +3686,19 @@
         <v>9</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J40">
         <v>-1</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L40">
         <v>-1</v>
@@ -3725,7 +3725,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>7</v>
@@ -3740,7 +3740,7 @@
         <v>9</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3754,7 +3754,7 @@
         <v>7</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3777,7 +3777,7 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C42">
         <v>5</v>
@@ -3795,16 +3795,16 @@
         <v>7</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J42">
         <v>-1</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L42">
         <v>-1</v>
@@ -3831,7 +3831,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U42">
         <v>5</v>
@@ -3872,22 +3872,22 @@
         <v>8</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -3911,19 +3911,19 @@
         <v>8</v>
       </c>
       <c r="U43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V43">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W43">
         <v>10</v>
       </c>
       <c r="X43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y43">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3979,7 +3979,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -3988,30 +3988,30 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>67.56999999999999</v>
+      </c>
+      <c r="G2">
+        <v>32.43</v>
+      </c>
+      <c r="H2">
+        <v>6.5</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>48.65</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="I2">
-        <v>19</v>
-      </c>
-      <c r="J2">
-        <v>51.35</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -4020,83 +4020,83 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>62.16</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>37.84</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>94.44</v>
+      </c>
+      <c r="G4">
+        <v>5.56</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>80</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>7.5</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>88.89</v>
+        <v>94.59</v>
       </c>
       <c r="G5">
-        <v>11.11</v>
+        <v>5.41</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4107,28 +4107,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>94.59</v>
+        <v>97.5</v>
       </c>
       <c r="G6">
-        <v>5.41</v>
+        <v>2.5</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4176,7 +4176,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4205,19 +4205,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920071</v>
+        <v>21330051920072</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>62</v>
@@ -4225,59 +4225,59 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920072</v>
+        <v>21330051920357</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920357</v>
+        <v>21330051920077</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920357</v>
+        <v>21330051920082</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>62</v>
@@ -4285,39 +4285,39 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920108</v>
+        <v>21330051920098</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920108</v>
+        <v>21330051920100</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>62</v>
@@ -4325,701 +4325,61 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920108</v>
+        <v>21330051920383</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920076</v>
+        <v>21330051920107</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920076</v>
+        <v>21330051920109</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920077</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920077</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" t="s">
-        <v>114</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920078</v>
-      </c>
-      <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920078</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920080</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920080</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920082</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920086</v>
-      </c>
-      <c r="B18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920302</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920092</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920092</v>
-      </c>
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" t="s">
-        <v>100</v>
-      </c>
-      <c r="D21" t="s">
-        <v>119</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920094</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" t="s">
-        <v>120</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920097</v>
-      </c>
-      <c r="B23" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" t="s">
-        <v>121</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920097</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" t="s">
-        <v>121</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>18330051920296</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" t="s">
-        <v>122</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920098</v>
-      </c>
-      <c r="B26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" t="s">
-        <v>123</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920098</v>
-      </c>
-      <c r="B27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920099</v>
-      </c>
-      <c r="B28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" t="s">
-        <v>124</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920100</v>
-      </c>
-      <c r="B29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" t="s">
-        <v>104</v>
-      </c>
-      <c r="D29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920100</v>
-      </c>
-      <c r="B30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30" t="s">
-        <v>125</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920383</v>
-      </c>
-      <c r="B31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" t="s">
-        <v>86</v>
-      </c>
-      <c r="D31" t="s">
-        <v>126</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920102</v>
-      </c>
-      <c r="B32" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" t="s">
-        <v>127</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920102</v>
-      </c>
-      <c r="B33" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" t="s">
-        <v>105</v>
-      </c>
-      <c r="D33" t="s">
-        <v>127</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920103</v>
-      </c>
-      <c r="B34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34" t="s">
-        <v>128</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920103</v>
-      </c>
-      <c r="B35" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" t="s">
-        <v>128</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920104</v>
-      </c>
-      <c r="B36" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D36" t="s">
-        <v>129</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920104</v>
-      </c>
-      <c r="B37" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" t="s">
-        <v>106</v>
-      </c>
-      <c r="D37" t="s">
-        <v>129</v>
-      </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920107</v>
-      </c>
-      <c r="B38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" t="s">
-        <v>130</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920107</v>
-      </c>
-      <c r="B39" t="s">
-        <v>89</v>
-      </c>
-      <c r="C39" t="s">
-        <v>107</v>
-      </c>
-      <c r="D39" t="s">
-        <v>130</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920107</v>
-      </c>
-      <c r="B40" t="s">
-        <v>89</v>
-      </c>
-      <c r="C40" t="s">
-        <v>107</v>
-      </c>
-      <c r="D40" t="s">
-        <v>130</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920109</v>
-      </c>
-      <c r="B41" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" t="s">
-        <v>108</v>
-      </c>
-      <c r="D41" t="s">
-        <v>131</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920109</v>
-      </c>
-      <c r="B42" t="s">
-        <v>90</v>
-      </c>
-      <c r="C42" t="s">
-        <v>108</v>
-      </c>
-      <c r="D42" t="s">
-        <v>131</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
         <v>62</v>
       </c>
     </row>
@@ -5056,421 +4416,421 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920108</v>
+        <v>21330051920072</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920107</v>
+        <v>21330051920357</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920357</v>
+        <v>21330051920077</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920076</v>
+        <v>21330051920082</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920077</v>
+        <v>21330051920098</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920078</v>
+        <v>21330051920100</v>
       </c>
       <c r="B7" t="s">
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920080</v>
+        <v>21330051920383</v>
       </c>
       <c r="B8" t="s">
         <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920092</v>
+        <v>21330051920107</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920097</v>
+        <v>21330051920109</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920098</v>
+        <v>21330051920071</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920100</v>
+        <v>21330051920074</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920102</v>
+        <v>20330051920378</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920103</v>
+        <v>21330051920075</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920104</v>
+        <v>21330051920108</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920109</v>
+        <v>21330051920076</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920071</v>
+        <v>21330051920078</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920072</v>
+        <v>21330051920079</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920082</v>
+        <v>21330051920080</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920086</v>
+        <v>21330051920081</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920302</v>
+        <v>21330051920083</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920094</v>
+        <v>21330051920084</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>18330051920296</v>
+        <v>21330051920085</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920099</v>
+        <v>21330051920086</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920383</v>
+        <v>20330051920302</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920074</v>
+        <v>21330051920089</v>
       </c>
       <c r="B26" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
         <v>152</v>
@@ -5481,13 +4841,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920378</v>
+        <v>21330051920092</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
         <v>153</v>
@@ -5498,13 +4858,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920075</v>
+        <v>21330051920093</v>
       </c>
       <c r="B28" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
         <v>154</v>
@@ -5515,13 +4875,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920079</v>
+        <v>21330051920094</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D29" t="s">
         <v>155</v>
@@ -5532,13 +4892,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920081</v>
+        <v>21330051920096</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
         <v>156</v>
@@ -5549,13 +4909,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920083</v>
+        <v>21330051920097</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="D31" t="s">
         <v>157</v>
@@ -5566,13 +4926,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920084</v>
+        <v>18330051920296</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
         <v>158</v>
@@ -5583,13 +4943,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920085</v>
+        <v>21330051920099</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s">
         <v>159</v>
@@ -5600,13 +4960,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920089</v>
+        <v>21330051920101</v>
       </c>
       <c r="B34" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s">
         <v>160</v>
@@ -5617,13 +4977,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920093</v>
+        <v>21330051920102</v>
       </c>
       <c r="B35" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D35" t="s">
         <v>161</v>
@@ -5634,13 +4994,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920096</v>
+        <v>21330051920103</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="C36" t="s">
-        <v>147</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
         <v>162</v>
@@ -5651,13 +5011,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920101</v>
+        <v>21330051920104</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
         <v>163</v>
@@ -5671,10 +5031,10 @@
         <v>21330051920105</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="C38" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
         <v>164</v>
@@ -5688,10 +5048,10 @@
         <v>21330051920106</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D39" t="s">
         <v>165</v>
@@ -5705,10 +5065,10 @@
         <v>18330051920309</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C40" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="D40" t="s">
         <v>166</v>
@@ -5722,10 +5082,10 @@
         <v>21330051920387</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="C41" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
         <v>167</v>
@@ -5741,7 +5101,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5773,45 +5133,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920357</v>
+        <v>21330051920072</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920357</v>
+        <v>21330051920072</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -5819,45 +5179,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920076</v>
+        <v>21330051920357</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920076</v>
+        <v>21330051920357</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5865,91 +5225,91 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920077</v>
+        <v>21330051920108</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920077</v>
+        <v>21330051920108</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920080</v>
+        <v>21330051920082</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>61</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920080</v>
+        <v>21330051920082</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -5957,45 +5317,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920092</v>
+        <v>21330051920098</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920092</v>
+        <v>21330051920098</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -6003,22 +5363,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920094</v>
+        <v>21330051920100</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6026,22 +5386,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920094</v>
+        <v>21330051920100</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -6049,45 +5409,45 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920097</v>
+        <v>21330051920071</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>61</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920097</v>
+        <v>21330051920077</v>
       </c>
       <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
         <v>82</v>
       </c>
-      <c r="C15" t="s">
-        <v>102</v>
-      </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -6095,65 +5455,65 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920098</v>
+        <v>21330051920078</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920098</v>
+        <v>21330051920094</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920100</v>
+        <v>21330051920383</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
         <v>62</v>
@@ -6164,370 +5524,71 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920100</v>
+        <v>21330051920102</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
         <v>61</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920102</v>
+        <v>21330051920103</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="E20" t="s">
         <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920102</v>
+        <v>21330051920104</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920103</v>
-      </c>
-      <c r="B22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" t="s">
-        <v>128</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920103</v>
-      </c>
-      <c r="B23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920104</v>
-      </c>
-      <c r="B24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" t="s">
-        <v>129</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920104</v>
-      </c>
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" t="s">
-        <v>129</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>61</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920071</v>
-      </c>
-      <c r="B26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" t="s">
-        <v>109</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920072</v>
-      </c>
-      <c r="B27" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>61</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920082</v>
-      </c>
-      <c r="B28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>61</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920085</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" t="s">
-        <v>95</v>
-      </c>
-      <c r="D29" t="s">
-        <v>159</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
-      </c>
-      <c r="G29">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920086</v>
-      </c>
-      <c r="B30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>63</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920302</v>
-      </c>
-      <c r="B31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>61</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>18330051920296</v>
-      </c>
-      <c r="B32" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" t="s">
-        <v>103</v>
-      </c>
-      <c r="D32" t="s">
-        <v>122</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>63</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920099</v>
-      </c>
-      <c r="B33" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" t="s">
-        <v>124</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>61</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920383</v>
-      </c>
-      <c r="B34" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" t="s">
-        <v>86</v>
-      </c>
-      <c r="D34" t="s">
-        <v>126</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>61</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ALCV - Estadisticos 20212.xlsx
+++ b/grupos/2ALCV - Estadisticos 20212.xlsx
@@ -1182,7 +1182,7 @@
         <v>5</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1673,7 +1673,7 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>9</v>
@@ -2135,7 +2135,7 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2171,7 +2171,7 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -2585,7 +2585,7 @@
         <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>8</v>
@@ -2816,7 +2816,7 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -3384,7 +3384,7 @@
         <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
         <v>9</v>
@@ -3461,7 +3461,7 @@
         <v>5</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
         <v>9</v>

--- a/grupos/2ALCV - Estadisticos 20212.xlsx
+++ b/grupos/2ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="168">
   <si>
     <t>Materia</t>
   </si>
@@ -203,19 +203,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Flores Ovalle Victor</t>
   </si>
   <si>
     <t>Rivera Serra Alma Lilian</t>
@@ -1043,10 +1043,10 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1055,13 +1055,13 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -1114,16 +1114,16 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1132,7 +1132,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1141,7 +1141,7 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -1191,16 +1191,16 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1209,16 +1209,16 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1227,7 +1227,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1274,10 +1274,10 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1286,7 +1286,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1304,7 +1304,7 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1380,10 +1380,10 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1392,13 +1392,13 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1410,7 +1410,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1457,25 +1457,25 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1534,37 +1534,37 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>8</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>6</v>
@@ -1605,16 +1605,16 @@
         <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1623,7 +1623,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1641,7 +1641,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1682,16 +1682,16 @@
         <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1700,7 +1700,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1709,7 +1709,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1759,16 +1759,16 @@
         <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1777,13 +1777,13 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>9</v>
@@ -1795,7 +1795,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1842,19 +1842,19 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1866,13 +1866,13 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1919,25 +1919,25 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -1990,16 +1990,16 @@
         <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2008,7 +2008,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2026,7 +2026,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2073,19 +2073,19 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2138,7 +2138,7 @@
         <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>10</v>
@@ -2150,28 +2150,28 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -2180,7 +2180,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2227,31 +2227,31 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>9</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2304,10 +2304,10 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2316,16 +2316,16 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2381,10 +2381,10 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2393,13 +2393,13 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>9</v>
@@ -2452,7 +2452,7 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2461,7 +2461,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2523,10 +2523,10 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2535,13 +2535,13 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2600,37 +2600,37 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>10</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>10</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2677,19 +2677,19 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2748,16 +2748,16 @@
         <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
         <v>-1</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2766,13 +2766,13 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>8</v>
@@ -2825,16 +2825,16 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>-1</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2843,13 +2843,13 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U28">
         <v>5</v>
@@ -2861,7 +2861,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -2908,19 +2908,19 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3008,16 +3008,16 @@
         <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
         <v>-1</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3026,7 +3026,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3035,7 +3035,7 @@
         <v>5</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>-1</v>
@@ -3044,7 +3044,7 @@
         <v>7</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -3085,25 +3085,25 @@
         <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>7</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3121,7 +3121,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3162,16 +3162,16 @@
         <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3180,13 +3180,13 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>8</v>
@@ -3198,7 +3198,7 @@
         <v>9</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>8</v>
@@ -3245,19 +3245,19 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3266,7 +3266,7 @@
         <v>6</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>9</v>
@@ -3275,7 +3275,7 @@
         <v>10</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3316,16 +3316,16 @@
         <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3334,7 +3334,7 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3393,16 +3393,16 @@
         <v>7</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3411,16 +3411,16 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -3429,7 +3429,7 @@
         <v>7</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3470,16 +3470,16 @@
         <v>9</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M37">
         <v>-1</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3488,7 +3488,7 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3547,16 +3547,16 @@
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M38">
         <v>8</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3565,16 +3565,16 @@
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S38">
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V38">
         <v>10</v>
@@ -3583,7 +3583,7 @@
         <v>7</v>
       </c>
       <c r="X38">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>8</v>
@@ -3630,19 +3630,19 @@
         <v>8</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -3654,7 +3654,7 @@
         <v>9</v>
       </c>
       <c r="V39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W39">
         <v>10</v>
@@ -3701,16 +3701,16 @@
         <v>7</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M40">
         <v>-1</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -3719,13 +3719,13 @@
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S40">
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U40">
         <v>7</v>
@@ -3737,7 +3737,7 @@
         <v>7</v>
       </c>
       <c r="X40">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -3807,16 +3807,16 @@
         <v>6</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M42">
         <v>-1</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -3825,16 +3825,16 @@
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S42">
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V42">
         <v>-1</v>
@@ -3843,7 +3843,7 @@
         <v>7</v>
       </c>
       <c r="X42">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y42">
         <v>7</v>
@@ -3890,19 +3890,19 @@
         <v>9</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q43">
         <v>-1</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S43">
         <v>-1</v>
@@ -3979,7 +3979,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -3988,30 +3988,30 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>67.56999999999999</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="G2">
-        <v>32.43</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -4020,25 +4020,25 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>89.19</v>
+      </c>
+      <c r="G3">
+        <v>10.81</v>
+      </c>
+      <c r="H3">
+        <v>6.5</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>75.68000000000001</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>24.32</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4052,16 +4052,16 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>94.44</v>
+        <v>97.22</v>
       </c>
       <c r="G4">
-        <v>5.56</v>
+        <v>2.78</v>
       </c>
       <c r="H4">
         <v>7.8</v>
@@ -4075,28 +4075,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>94.59</v>
+        <v>97.5</v>
       </c>
       <c r="G5">
-        <v>5.41</v>
+        <v>2.5</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4107,25 +4107,25 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>7.5</v>
@@ -4220,7 +4220,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4240,7 +4240,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4260,7 +4260,7 @@
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4280,7 +4280,7 @@
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4300,7 +4300,7 @@
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4320,7 +4320,7 @@
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4340,7 +4340,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4360,7 +4360,7 @@
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4380,7 +4380,7 @@
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -5101,7 +5101,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5133,22 +5133,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920072</v>
+        <v>21330051920357</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5156,22 +5156,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920072</v>
+        <v>21330051920357</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -5179,22 +5179,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920357</v>
+        <v>21330051920094</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5202,45 +5202,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920357</v>
+        <v>21330051920094</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920108</v>
+        <v>21330051920098</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5248,114 +5248,114 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920108</v>
+        <v>21330051920098</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920082</v>
+        <v>21330051920107</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>61</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920082</v>
+        <v>21330051920107</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920098</v>
+        <v>21330051920072</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>61</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920098</v>
+        <v>21330051920077</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -5363,25 +5363,25 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920100</v>
+        <v>21330051920082</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>61</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5401,7 +5401,7 @@
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -5409,186 +5409,71 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920071</v>
+        <v>21330051920383</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
         <v>61</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920077</v>
+        <v>21330051920103</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
         <v>62</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920078</v>
+        <v>21330051920109</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920094</v>
-      </c>
-      <c r="B17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" t="s">
-        <v>129</v>
-      </c>
-      <c r="D17" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920383</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920102</v>
-      </c>
-      <c r="B19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" t="s">
-        <v>161</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920103</v>
-      </c>
-      <c r="B20" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" t="s">
-        <v>162</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920104</v>
-      </c>
-      <c r="B21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C21" t="s">
-        <v>133</v>
-      </c>
-      <c r="D21" t="s">
-        <v>163</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ALCV - Estadisticos 20212.xlsx
+++ b/grupos/2ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="168">
   <si>
     <t>Materia</t>
   </si>
@@ -212,12 +212,12 @@
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
@@ -233,292 +233,292 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>CHACÓN</t>
   </si>
   <si>
     <t>CABALLERO</t>
   </si>
   <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>ELPIDIO</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>RUGERIO</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
     <t>TENTZOHUA</t>
   </si>
   <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
     <t>LEYVA</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>LAGUNES</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
     <t>BRETON</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
   </si>
   <si>
     <t>LEÓN</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
     <t>KATHIA</t>
   </si>
   <si>
     <t>LUIS ARMANDO</t>
   </si>
   <si>
+    <t>CRISTAL YOSELIN</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>BERENICE</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
     <t>VANESSA AMAIRANY</t>
   </si>
   <si>
+    <t>REGINA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>FATIMA MARILYN</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ITZEL ABIGAIL</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
     <t>ALDO GEOVANNI</t>
   </si>
   <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
     <t>ALONDRA YURIDIA</t>
   </si>
   <si>
+    <t>CITLALI ESPERANZA</t>
+  </si>
+  <si>
     <t>KIMBERLY</t>
   </si>
   <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
     <t>RUBI</t>
   </si>
   <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
     <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>ELPIDIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>CRISTAL YOSELIN</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>MARYFER</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
-  </si>
-  <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>FLOR GUADALUPE</t>
@@ -1049,16 +1049,16 @@
         <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>6</v>
@@ -1090,7 +1090,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>8</v>
@@ -1108,16 +1108,16 @@
         <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>5</v>
@@ -1126,16 +1126,16 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
         <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>5</v>
@@ -1144,10 +1144,10 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -1167,7 +1167,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>8</v>
@@ -1185,16 +1185,16 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>7</v>
@@ -1203,16 +1203,16 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
         <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>6</v>
@@ -1221,10 +1221,10 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>6</v>
@@ -1280,16 +1280,16 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1298,7 +1298,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1324,19 +1324,19 @@
         <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1350,7 +1350,7 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>9</v>
@@ -1368,7 +1368,7 @@
         <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>8</v>
@@ -1386,16 +1386,16 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
         <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>6</v>
@@ -1404,10 +1404,10 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1466,13 +1466,13 @@
         <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
         <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>6</v>
@@ -1543,13 +1543,13 @@
         <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>6</v>
@@ -1567,7 +1567,7 @@
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1599,7 +1599,7 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>9</v>
@@ -1617,16 +1617,16 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>6</v>
@@ -1635,10 +1635,10 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1694,16 +1694,16 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
         <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1712,7 +1712,7 @@
         <v>6</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1735,7 +1735,7 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>9</v>
@@ -1753,7 +1753,7 @@
         <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
         <v>7</v>
@@ -1762,7 +1762,7 @@
         <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -1771,16 +1771,16 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>6</v>
@@ -1789,7 +1789,7 @@
         <v>9</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1851,13 +1851,13 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>6</v>
@@ -1928,13 +1928,13 @@
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -2002,16 +2002,16 @@
         <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -2020,7 +2020,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2029,7 +2029,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2064,7 +2064,7 @@
         <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>8</v>
@@ -2082,13 +2082,13 @@
         <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
         <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -2100,7 +2100,7 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2159,13 +2159,13 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>6</v>
@@ -2236,13 +2236,13 @@
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2292,7 +2292,7 @@
         <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>8</v>
@@ -2310,16 +2310,16 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>6</v>
@@ -2328,7 +2328,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2387,16 +2387,16 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2405,16 +2405,16 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2455,16 +2455,16 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>6</v>
@@ -2529,16 +2529,16 @@
         <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2547,7 +2547,7 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2609,13 +2609,13 @@
         <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
         <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2627,7 +2627,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -2686,13 +2686,13 @@
         <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>8</v>
@@ -2751,7 +2751,7 @@
         <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>6</v>
@@ -2760,16 +2760,16 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>6</v>
@@ -2787,7 +2787,7 @@
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2819,16 +2819,16 @@
         <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>5</v>
@@ -2837,16 +2837,16 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
         <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>5</v>
@@ -2855,16 +2855,16 @@
         <v>5</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2917,13 +2917,13 @@
         <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -2941,7 +2941,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2961,10 +2961,10 @@
         <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -2984,7 +2984,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>7</v>
@@ -3002,7 +3002,7 @@
         <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
         <v>7</v>
@@ -3011,7 +3011,7 @@
         <v>5</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>5</v>
@@ -3020,16 +3020,16 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
         <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>5</v>
@@ -3038,7 +3038,7 @@
         <v>6</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>7</v>
@@ -3100,13 +3100,13 @@
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
         <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>6</v>
@@ -3118,13 +3118,13 @@
         <v>8</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3138,7 +3138,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E33">
         <v>8</v>
@@ -3156,7 +3156,7 @@
         <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>9</v>
@@ -3174,16 +3174,16 @@
         <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
         <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>6</v>
@@ -3192,10 +3192,10 @@
         <v>8</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>7</v>
@@ -3254,13 +3254,13 @@
         <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>6</v>
@@ -3278,7 +3278,7 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3292,7 +3292,7 @@
         <v>8</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E35">
         <v>9</v>
@@ -3310,7 +3310,7 @@
         <v>8</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
         <v>8</v>
@@ -3328,16 +3328,16 @@
         <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
         <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>7</v>
@@ -3346,10 +3346,10 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>8</v>
@@ -3405,16 +3405,16 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
         <v>6</v>
@@ -3423,7 +3423,7 @@
         <v>6</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3473,7 +3473,7 @@
         <v>6</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>5</v>
@@ -3482,16 +3482,16 @@
         <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R37">
         <v>6</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
         <v>5</v>
@@ -3500,10 +3500,10 @@
         <v>10</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>6</v>
@@ -3544,7 +3544,7 @@
         <v>9</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L38">
         <v>5</v>
@@ -3559,16 +3559,16 @@
         <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R38">
         <v>5</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T38">
         <v>6</v>
@@ -3577,16 +3577,16 @@
         <v>6</v>
       </c>
       <c r="V38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X38">
         <v>6</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3639,13 +3639,13 @@
         <v>7</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>9</v>
@@ -3663,7 +3663,7 @@
         <v>10</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3677,7 +3677,7 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E40">
         <v>7</v>
@@ -3695,7 +3695,7 @@
         <v>7</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K40">
         <v>7</v>
@@ -3704,7 +3704,7 @@
         <v>5</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N40">
         <v>7</v>
@@ -3713,16 +3713,16 @@
         <v>7</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R40">
         <v>7</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
         <v>6</v>
@@ -3731,7 +3731,7 @@
         <v>7</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W40">
         <v>7</v>
@@ -3740,7 +3740,7 @@
         <v>7</v>
       </c>
       <c r="Y40">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3757,13 +3757,13 @@
         <v>8</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W41">
         <v>8</v>
@@ -3783,7 +3783,7 @@
         <v>5</v>
       </c>
       <c r="D42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E42">
         <v>7</v>
@@ -3801,7 +3801,7 @@
         <v>6</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K42">
         <v>6</v>
@@ -3810,7 +3810,7 @@
         <v>5</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N42">
         <v>8</v>
@@ -3819,16 +3819,16 @@
         <v>7</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R42">
         <v>5</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T42">
         <v>6</v>
@@ -3837,10 +3837,10 @@
         <v>6</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X42">
         <v>6</v>
@@ -3899,13 +3899,13 @@
         <v>10</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R43">
         <v>9</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T43">
         <v>8</v>
@@ -3988,25 +3988,25 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>75.68000000000001</v>
+        <v>81.08</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>18.92</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>24.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4075,25 +4075,25 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>7.5</v>
@@ -4107,16 +4107,16 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4176,7 +4176,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4201,186 +4201,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920072</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920357</v>
-      </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920077</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920082</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920098</v>
-      </c>
-      <c r="B6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920100</v>
-      </c>
-      <c r="B7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920383</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920107</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920109</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4416,166 +4236,166 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920072</v>
+        <v>21330051920071</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920357</v>
+        <v>21330051920072</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920077</v>
+        <v>21330051920357</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920082</v>
+        <v>21330051920074</v>
       </c>
       <c r="B5" t="s">
         <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920098</v>
+        <v>20330051920378</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920100</v>
+        <v>21330051920075</v>
       </c>
       <c r="B7" t="s">
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920383</v>
+        <v>21330051920108</v>
       </c>
       <c r="B8" t="s">
         <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920107</v>
+        <v>21330051920076</v>
       </c>
       <c r="B9" t="s">
         <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920109</v>
+        <v>21330051920077</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920071</v>
+        <v>21330051920078</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
         <v>138</v>
@@ -4586,13 +4406,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920074</v>
+        <v>21330051920079</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
         <v>139</v>
@@ -4603,16 +4423,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920378</v>
+        <v>21330051920080</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4620,16 +4440,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920075</v>
+        <v>21330051920081</v>
       </c>
       <c r="B14" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4637,16 +4457,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920108</v>
+        <v>21330051920082</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4654,16 +4474,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920076</v>
+        <v>21330051920083</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4671,16 +4491,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920078</v>
+        <v>21330051920084</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4688,16 +4508,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920079</v>
+        <v>21330051920085</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4705,16 +4525,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920080</v>
+        <v>21330051920086</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4722,13 +4542,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920081</v>
+        <v>20330051920302</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
         <v>146</v>
@@ -4739,13 +4559,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920083</v>
+        <v>21330051920089</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
         <v>147</v>
@@ -4756,13 +4576,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920084</v>
+        <v>21330051920092</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
         <v>148</v>
@@ -4773,13 +4593,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920085</v>
+        <v>21330051920093</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
         <v>149</v>
@@ -4790,13 +4610,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920086</v>
+        <v>21330051920094</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
         <v>150</v>
@@ -4807,13 +4627,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920302</v>
+        <v>21330051920096</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
         <v>151</v>
@@ -4824,13 +4644,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920089</v>
+        <v>21330051920097</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
         <v>152</v>
@@ -4841,13 +4661,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920092</v>
+        <v>18330051920296</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
         <v>153</v>
@@ -4858,13 +4678,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920093</v>
+        <v>21330051920098</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
         <v>154</v>
@@ -4875,13 +4695,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920094</v>
+        <v>21330051920099</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
         <v>155</v>
@@ -4892,13 +4712,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920096</v>
+        <v>21330051920100</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
         <v>156</v>
@@ -4909,13 +4729,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920097</v>
+        <v>21330051920101</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
         <v>157</v>
@@ -4926,13 +4746,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>18330051920296</v>
+        <v>21330051920383</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s">
         <v>158</v>
@@ -4943,13 +4763,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920099</v>
+        <v>21330051920102</v>
       </c>
       <c r="B33" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" t="s">
         <v>75</v>
-      </c>
-      <c r="C33" t="s">
-        <v>110</v>
       </c>
       <c r="D33" t="s">
         <v>159</v>
@@ -4960,13 +4780,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920101</v>
+        <v>21330051920103</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D34" t="s">
         <v>160</v>
@@ -4977,13 +4797,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920102</v>
+        <v>21330051920104</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
         <v>161</v>
@@ -4994,13 +4814,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920103</v>
+        <v>21330051920105</v>
       </c>
       <c r="B36" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="D36" t="s">
         <v>162</v>
@@ -5011,13 +4831,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920104</v>
+        <v>21330051920106</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D37" t="s">
         <v>163</v>
@@ -5028,13 +4848,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920105</v>
+        <v>21330051920107</v>
       </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D38" t="s">
         <v>164</v>
@@ -5045,13 +4865,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920106</v>
+        <v>18330051920309</v>
       </c>
       <c r="B39" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D39" t="s">
         <v>165</v>
@@ -5062,13 +4882,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>18330051920309</v>
+        <v>21330051920109</v>
       </c>
       <c r="B40" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D40" t="s">
         <v>166</v>
@@ -5082,10 +4902,10 @@
         <v>21330051920387</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D41" t="s">
         <v>167</v>
@@ -5101,7 +4921,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5136,13 +4956,13 @@
         <v>21330051920357</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5159,13 +4979,13 @@
         <v>21330051920357</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -5174,7 +4994,7 @@
         <v>61</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5182,13 +5002,13 @@
         <v>21330051920094</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5205,13 +5025,13 @@
         <v>21330051920094</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -5228,13 +5048,13 @@
         <v>21330051920098</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
         <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5251,13 +5071,13 @@
         <v>21330051920098</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
         <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -5266,21 +5086,21 @@
         <v>61</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920107</v>
+        <v>21330051920072</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5289,27 +5109,27 @@
         <v>61</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920107</v>
+        <v>21330051920082</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5317,16 +5137,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920072</v>
+        <v>21330051920085</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5335,44 +5155,44 @@
         <v>61</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920077</v>
+        <v>21330051920103</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920082</v>
+        <v>21330051920107</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>164</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -5381,21 +5201,21 @@
         <v>61</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920100</v>
+        <v>21330051920109</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>166</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -5404,76 +5224,7 @@
         <v>61</v>
       </c>
       <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920383</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920103</v>
-      </c>
-      <c r="B15" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" t="s">
-        <v>162</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920109</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" t="s">
-        <v>97</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
